--- a/files/港岛-山顶区-Mount Nicholson I.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson I.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,16 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -223,10 +233,10 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +617,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-山顶区-Mount Nicholson I.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson I.xlsx
@@ -617,7 +617,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-山顶区-Mount Nicholson I.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson I.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,10 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -677,6 +681,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -723,6 +747,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -769,6 +813,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -815,6 +879,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -861,6 +945,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -907,6 +1011,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -953,6 +1077,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -999,6 +1143,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1045,6 +1209,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1091,6 +1275,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1137,6 +1341,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1183,6 +1407,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1229,6 +1473,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1275,6 +1539,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1321,6 +1605,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1367,6 +1671,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1413,6 +1737,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1463,13 +1807,33 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1612,7 +1976,7 @@
         <is>
           <t>1号屋
 9950呎 (4+房)
-(17年-01月)
+(17年-01月-22日)
 $10.80亿
 $108,543/呎</t>
         </is>
@@ -1621,7 +1985,7 @@
         <is>
           <t>2号屋
 9217呎 (4+房)
-(18年-04月)
+(18年-04月-15日)
 $13.99亿
 $151,785/呎</t>
         </is>
@@ -1630,7 +1994,7 @@
         <is>
           <t>3号屋
 9178呎 (4+房)
-(17年-11月)
+(17年-11月-23日)
 $11.64亿
 $126,813/呎</t>
         </is>
@@ -1639,7 +2003,7 @@
         <is>
           <t>5号屋
 9173呎 (4+房)
-(16年-05月)
+(16年-05月-05日)
 $7.40亿
 $80,672/呎</t>
         </is>
@@ -1648,7 +2012,7 @@
         <is>
           <t>6号屋
 9455呎 (4+房)
-(16年-03月)
+(16年-03月-15日)
 $8.30亿
 $87,784/呎</t>
         </is>
@@ -1657,7 +2021,7 @@
         <is>
           <t>7号屋
 8087呎 (4+房)
-(17年-03月)
+(17年-03月-12日)
 $7.20亿
 $89,032/呎</t>
         </is>
@@ -1673,7 +2037,7 @@
         <is>
           <t>8号屋
 8054呎 (4+房)
-(16年-08月)
+(16年-08月-15日)
 $6.30亿
 $78,222/呎</t>
         </is>
@@ -1682,7 +2046,7 @@
         <is>
           <t>9号屋
 8083呎 (4+房)
-(16年-12月)
+(16年-12月-12日)
 $6.00亿
 $74,230/呎</t>
         </is>
@@ -1691,7 +2055,7 @@
         <is>
           <t>10号屋
 8017呎 (4+房)
-(17年-06月)
+(17年-06月-05日)
 $6.64亿
 $82,809/呎</t>
         </is>
@@ -1700,7 +2064,7 @@
         <is>
           <t>11号屋
 7065呎 (3房)
-(16年-12月)
+(16年-12月-13日)
 $5.25亿
 $74,310/呎</t>
         </is>
@@ -1709,7 +2073,7 @@
         <is>
           <t>12号屋
 7042呎 (4+房)
-(23年-05月)
+(23年-05月-15日)
 $5.77亿
 $82,000/呎</t>
         </is>
@@ -1718,7 +2082,7 @@
         <is>
           <t>15号屋
 8674呎 (4+房)
-(19年-06月)
+(19年-06月-24日)
 $9.16亿
 $105,603/呎</t>
         </is>
@@ -1734,7 +2098,7 @@
         <is>
           <t>16号屋
 7978呎 (4+房)
-(19年-06月)
+(19年-06月-02日)
 $7.20亿
 $90,248/呎</t>
         </is>
@@ -1743,7 +2107,7 @@
         <is>
           <t>17号屋
 7984呎 (3房)
-(18年-04月)
+(18年-04月-26日)
 $7.80亿
 $97,695/呎</t>
         </is>
@@ -1752,7 +2116,7 @@
         <is>
           <t>18号屋
 8050呎 (4+房)
-(17年-08月)
+(17年-08月-16日)
 $6.45亿
 $80,124/呎</t>
         </is>
@@ -1761,7 +2125,7 @@
         <is>
           <t>19号屋
 7981呎 (4+房)
-(17年-09月)
+(17年-09月-19日)
 $6.20亿
 $77,685/呎</t>
         </is>

--- a/files/港岛-山顶区-Mount Nicholson I.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson I.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1500,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>16号屋</t>
+          <t>17号屋</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7978</v>
+        <v>7984</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1528,14 +1528,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2019-06-02</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>720000000</v>
+        <v>780000000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>90248</v>
+        <v>97695</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>17号屋</t>
+          <t>18号屋</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1581,11 +1581,11 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7984</v>
+        <v>8050</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1594,14 +1594,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>780000000</v>
+        <v>645000000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>97695</v>
+        <v>80124</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>18号屋</t>
+          <t>19号屋</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>8050</v>
+        <v>7981</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1660,14 +1660,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2017-08-16</t>
+          <t>2017-09-19</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>645000000</v>
+        <v>620000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>80124</v>
+        <v>77685</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>19号屋</t>
+          <t>20号屋</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1717,23 +1717,27 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7981</v>
+        <v>8093</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2017-09-19</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>620000000</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>77685</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1756,76 +1760,6 @@
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>20号屋</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>8093</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1900,7 +1834,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>17 套</t>
+          <t>16 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1915,7 +1849,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>16 套</t>
+          <t>15 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2096,15 +2030,6 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>16号屋
-7978呎 (4+房)
-(19年-06月-02日)
-$7.20亿
-$90,248/呎</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
           <t>17号屋
 7984呎 (3房)
 (18年-04月-26日)
@@ -2112,7 +2037,7 @@
 $97,695/呎</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>18号屋
 8050呎 (4+房)
@@ -2121,7 +2046,7 @@
 $80,124/呎</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>19号屋
 7981呎 (4+房)
@@ -2130,7 +2055,7 @@
 $77,685/呎</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>20号屋
 8093呎 (4+房)
@@ -2139,6 +2064,7 @@
 暂无呎价</t>
         </is>
       </c>
+      <c r="F8" s="18" t="inlineStr"/>
       <c r="G8" s="18" t="inlineStr"/>
     </row>
   </sheetData>

--- a/files/港岛-山顶区-Mount Nicholson I.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson I.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1500,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>17号屋</t>
+          <t>16号屋</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7984</v>
+        <v>7978</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1528,14 +1528,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2019-06-02</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>780000000</v>
+        <v>720000000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>97695</v>
+        <v>90248</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>18号屋</t>
+          <t>17号屋</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1581,11 +1581,11 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8050</v>
+        <v>7984</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1594,14 +1594,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2017-08-16</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>645000000</v>
+        <v>780000000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>80124</v>
+        <v>97695</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>19号屋</t>
+          <t>18号屋</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7981</v>
+        <v>8050</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1660,14 +1660,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2017-09-19</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>620000000</v>
+        <v>645000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>77685</v>
+        <v>80124</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1698,68 +1698,134 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>19号屋</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>7981</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>2017-09-19</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>77685</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>20号屋</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>8093</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1834,22 +1900,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>17 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>16 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>15 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1910,7 +1976,7 @@
         <is>
           <t>1号屋
 9950呎 (4+房)
-(17年-01月-22日)
+(17年-01月)
 $10.80亿
 $108,543/呎</t>
         </is>
@@ -1919,7 +1985,7 @@
         <is>
           <t>2号屋
 9217呎 (4+房)
-(18年-04月-15日)
+(18年-04月)
 $13.99亿
 $151,785/呎</t>
         </is>
@@ -1928,7 +1994,7 @@
         <is>
           <t>3号屋
 9178呎 (4+房)
-(17年-11月-23日)
+(17年-11月)
 $11.64亿
 $126,813/呎</t>
         </is>
@@ -1937,7 +2003,7 @@
         <is>
           <t>5号屋
 9173呎 (4+房)
-(16年-05月-05日)
+(16年-05月)
 $7.40亿
 $80,672/呎</t>
         </is>
@@ -1946,7 +2012,7 @@
         <is>
           <t>6号屋
 9455呎 (4+房)
-(16年-03月-15日)
+(16年-03月)
 $8.30亿
 $87,784/呎</t>
         </is>
@@ -1955,7 +2021,7 @@
         <is>
           <t>7号屋
 8087呎 (4+房)
-(17年-03月-12日)
+(17年-03月)
 $7.20亿
 $89,032/呎</t>
         </is>
@@ -1971,7 +2037,7 @@
         <is>
           <t>8号屋
 8054呎 (4+房)
-(16年-08月-15日)
+(16年-08月)
 $6.30亿
 $78,222/呎</t>
         </is>
@@ -1980,7 +2046,7 @@
         <is>
           <t>9号屋
 8083呎 (4+房)
-(16年-12月-12日)
+(16年-12月)
 $6.00亿
 $74,230/呎</t>
         </is>
@@ -1989,7 +2055,7 @@
         <is>
           <t>10号屋
 8017呎 (4+房)
-(17年-06月-05日)
+(17年-06月)
 $6.64亿
 $82,809/呎</t>
         </is>
@@ -1998,7 +2064,7 @@
         <is>
           <t>11号屋
 7065呎 (3房)
-(16年-12月-13日)
+(16年-12月)
 $5.25亿
 $74,310/呎</t>
         </is>
@@ -2007,7 +2073,7 @@
         <is>
           <t>12号屋
 7042呎 (4+房)
-(23年-05月-15日)
+(23年-05月)
 $5.77亿
 $82,000/呎</t>
         </is>
@@ -2016,7 +2082,7 @@
         <is>
           <t>15号屋
 8674呎 (4+房)
-(19年-06月-24日)
+(19年-06月)
 $9.16亿
 $105,603/呎</t>
         </is>
@@ -2030,32 +2096,41 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
+          <t>16号屋
+7978呎 (4+房)
+(19年-06月)
+$7.20亿
+$90,248/呎</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
           <t>17号屋
 7984呎 (3房)
-(18年-04月-26日)
+(18年-04月)
 $7.80亿
 $97,695/呎</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>18号屋
 8050呎 (4+房)
-(17年-08月-16日)
+(17年-08月)
 $6.45亿
 $80,124/呎</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>19号屋
 7981呎 (4+房)
-(17年-09月-19日)
+(17年-09月)
 $6.20亿
 $77,685/呎</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>20号屋
 8093呎 (4+房)
@@ -2064,7 +2139,6 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr"/>
       <c r="G8" s="18" t="inlineStr"/>
     </row>
   </sheetData>

--- a/files/港岛-山顶区-Mount Nicholson I.xlsx
+++ b/files/港岛-山顶区-Mount Nicholson I.xlsx
@@ -1976,7 +1976,7 @@
         <is>
           <t>1号屋
 9950呎 (4+房)
-(17年-01月)
+(17年-01月-22日)
 $10.80亿
 $108,543/呎</t>
         </is>
@@ -1985,7 +1985,7 @@
         <is>
           <t>2号屋
 9217呎 (4+房)
-(18年-04月)
+(18年-04月-15日)
 $13.99亿
 $151,785/呎</t>
         </is>
@@ -1994,7 +1994,7 @@
         <is>
           <t>3号屋
 9178呎 (4+房)
-(17年-11月)
+(17年-11月-23日)
 $11.64亿
 $126,813/呎</t>
         </is>
@@ -2003,7 +2003,7 @@
         <is>
           <t>5号屋
 9173呎 (4+房)
-(16年-05月)
+(16年-05月-05日)
 $7.40亿
 $80,672/呎</t>
         </is>
@@ -2012,7 +2012,7 @@
         <is>
           <t>6号屋
 9455呎 (4+房)
-(16年-03月)
+(16年-03月-15日)
 $8.30亿
 $87,784/呎</t>
         </is>
@@ -2021,7 +2021,7 @@
         <is>
           <t>7号屋
 8087呎 (4+房)
-(17年-03月)
+(17年-03月-12日)
 $7.20亿
 $89,032/呎</t>
         </is>
@@ -2037,7 +2037,7 @@
         <is>
           <t>8号屋
 8054呎 (4+房)
-(16年-08月)
+(16年-08月-15日)
 $6.30亿
 $78,222/呎</t>
         </is>
@@ -2046,7 +2046,7 @@
         <is>
           <t>9号屋
 8083呎 (4+房)
-(16年-12月)
+(16年-12月-12日)
 $6.00亿
 $74,230/呎</t>
         </is>
@@ -2055,7 +2055,7 @@
         <is>
           <t>10号屋
 8017呎 (4+房)
-(17年-06月)
+(17年-06月-05日)
 $6.64亿
 $82,809/呎</t>
         </is>
@@ -2064,7 +2064,7 @@
         <is>
           <t>11号屋
 7065呎 (3房)
-(16年-12月)
+(16年-12月-13日)
 $5.25亿
 $74,310/呎</t>
         </is>
@@ -2073,7 +2073,7 @@
         <is>
           <t>12号屋
 7042呎 (4+房)
-(23年-05月)
+(23年-05月-15日)
 $5.77亿
 $82,000/呎</t>
         </is>
@@ -2082,7 +2082,7 @@
         <is>
           <t>15号屋
 8674呎 (4+房)
-(19年-06月)
+(19年-06月-24日)
 $9.16亿
 $105,603/呎</t>
         </is>
@@ -2098,7 +2098,7 @@
         <is>
           <t>16号屋
 7978呎 (4+房)
-(19年-06月)
+(19年-06月-02日)
 $7.20亿
 $90,248/呎</t>
         </is>
@@ -2107,7 +2107,7 @@
         <is>
           <t>17号屋
 7984呎 (3房)
-(18年-04月)
+(18年-04月-26日)
 $7.80亿
 $97,695/呎</t>
         </is>
@@ -2116,7 +2116,7 @@
         <is>
           <t>18号屋
 8050呎 (4+房)
-(17年-08月)
+(17年-08月-16日)
 $6.45亿
 $80,124/呎</t>
         </is>
@@ -2125,7 +2125,7 @@
         <is>
           <t>19号屋
 7981呎 (4+房)
-(17年-09月)
+(17年-09月-19日)
 $6.20亿
 $77,685/呎</t>
         </is>
